--- a/data/trans_orig/IP07A17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52208</t>
+          <t>51803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71021</t>
+          <t>69932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54317</t>
+          <t>53774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72938</t>
+          <t>72163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110019</t>
+          <t>110675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139024</t>
+          <t>138555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40073</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58391</t>
+          <t>57578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51456</t>
+          <t>52373</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69864</t>
+          <t>70623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96183</t>
+          <t>94692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122925</t>
+          <t>122088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>8855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18844</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19473</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85750</t>
+          <t>86135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108177</t>
+          <t>108448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92383</t>
+          <t>92304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114839</t>
+          <t>115215</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185723</t>
+          <t>185436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216439</t>
+          <t>217435</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66989</t>
+          <t>67596</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89396</t>
+          <t>89086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71672</t>
+          <t>71001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92897</t>
+          <t>93212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144587</t>
+          <t>143672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175752</t>
+          <t>175707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18816</t>
+          <t>19252</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>36522</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172006</t>
+          <t>171182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>152519</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>182295</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305050</t>
+          <t>304942</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344854</t>
+          <t>344240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>127169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>158308</t>
+          <t>157582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249463</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>289981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43777</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>66589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68503</t>
+          <t>68647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88742</t>
+          <t>89270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89924</t>
+          <t>90760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144876</t>
+          <t>144654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174308</t>
+          <t>173501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57678</t>
+          <t>56342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78408</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48415</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68824</t>
+          <t>67483</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108598</t>
+          <t>109706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138711</t>
+          <t>138541</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,47%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>23337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18301</t>
+          <t>18429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>7162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74195</t>
+          <t>73902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95127</t>
+          <t>95398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>86990</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>108519</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>165045</t>
+          <t>168240</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197292</t>
+          <t>198954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49810</t>
+          <t>49379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70491</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>57120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>77764</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112775</t>
+          <t>112611</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142534</t>
+          <t>142718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27539</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149047</t>
+          <t>148993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>178784</t>
+          <t>177753</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>162006</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>193089</t>
+          <t>191181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320082</t>
+          <t>320716</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>363289</t>
+          <t>364353</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>112005</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141238</t>
+          <t>140418</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>111806</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>138869</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>232619</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>271028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97335</t>
+          <t>97854</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119474</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>93737</t>
+          <t>94054</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116179</t>
+          <t>116436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198937</t>
+          <t>198510</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>230702</t>
+          <t>229795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,09%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>51155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73138</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48982</t>
+          <t>48203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106139</t>
+          <t>106406</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136236</t>
+          <t>134712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16388</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7961</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>16396</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31499</t>
+          <t>32838</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>724</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6505</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75382</t>
+          <t>77101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97449</t>
+          <t>98115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84721</t>
+          <t>84055</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107612</t>
+          <t>107279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167922</t>
+          <t>167135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198772</t>
+          <t>199388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>58637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79897</t>
+          <t>78660</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49142</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69714</t>
+          <t>69249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111020</t>
+          <t>111252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141358</t>
+          <t>143974</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16904</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7817</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>32430</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>180801</t>
+          <t>181307</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>211375</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>185812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>215282</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373874</t>
+          <t>373451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419120</t>
+          <t>420754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114830</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144470</t>
+          <t>145909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103881</t>
+          <t>102355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132224</t>
+          <t>130885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>225974</t>
+          <t>224757</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268154</t>
+          <t>269772</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A17-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>62910</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>54214</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72923</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>60816</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>51803</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>69932</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>51793</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>69618</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,2%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>41,05%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>62910</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>53774</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>72163</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,58%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>38,96%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110675</t>
+          <t>110222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138555</t>
+          <t>136371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61011</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51158</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69972</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48982</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40308</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57578</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40243</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58407</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,82%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,63%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61011</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52373</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70623</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94692</t>
+          <t>97919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122088</t>
+          <t>124621</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12762</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8161</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>13693</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8855</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20118</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9086</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>20357</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12762</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7863</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19357</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>34788</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1912</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>537</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5538</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3423</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1179,102 +1179,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3236</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4251</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4480</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1426</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4554</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1426</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4954</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>138015</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>138015</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>138015</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126182</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126182</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126182</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>138015</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>138015</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>138015</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,64 +1404,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104092</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93748</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>115720</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,19%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>46,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>97189</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>86135</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>108448</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86092</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>108728</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104092</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>92304</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>115215</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>45,39%</t>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185436</t>
+          <t>186020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217435</t>
+          <t>217129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>81463</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70705</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>92384</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77883</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67596</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89086</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66688</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89357</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>41,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>35,64%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>81463</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>71001</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>93212</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143672</t>
+          <t>144728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175707</t>
+          <t>173745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15089</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9950</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22107</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12644</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7999</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19252</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7760</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19467</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,67%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,22%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>15089</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9713</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21798</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>36970</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4022</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5091</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5504</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7452</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3771</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>647</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3246</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>4314</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3965</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4064</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203352</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203352</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203352</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>189688</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>189688</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>189688</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203352</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203352</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203352</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>167002</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>153068</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>181278</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>158005</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>143213</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>171182</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>143602</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>171284</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,19%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>167002</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>152519</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>182295</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304942</t>
+          <t>303123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344240</t>
+          <t>344636</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142474</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>128918</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>156647</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>41,74%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>45,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>126865</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>113682</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>141886</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113858</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>141124</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,16%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,92%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>142474</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>127169</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>157582</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>41,74%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248856</t>
+          <t>249691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>289981</t>
+          <t>289851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -2312,64 +2312,64 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27851</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20710</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>36982</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26337</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18580</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34398</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19135</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>35219</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>27851</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20677</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>36560</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>44681</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>66589</t>
+          <t>67164</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6825</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3237</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1212</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2726</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6814</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -2543,67 +2543,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3965</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1425</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4603</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4388</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>341367</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>341367</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>341367</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>469</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>315869</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>315869</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>315869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>341367</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>341367</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>341367</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80270</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69422</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>90549</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>57,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>78739</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>68647</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89270</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>69201</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>89351</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>50,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>44,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>80270</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>69644</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>90760</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144654</t>
+          <t>144848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>173228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57413</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47519</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68721</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,86%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66715</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56342</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76962</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56382</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76132</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,7%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57413</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>47464</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>67483</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109706</t>
+          <t>109636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138541</t>
+          <t>138695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9811</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22890</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,26%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9400</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5498</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15907</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5130</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15646</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,07%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>16090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10645</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23337</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>18365</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>34672</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -3337,84 +3337,84 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7182</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>2902</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7162</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>2902</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
           <t>775</t>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>154854</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>154854</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>154854</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>97818</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>87193</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>108084</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50,15%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>84757</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73902</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>95398</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>74657</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>95676</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>97818</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>87409</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>108519</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,26%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>168240</t>
+          <t>168756</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198954</t>
+          <t>198417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67274</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57255</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>59885</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>49379</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>69567</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>49951</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69031</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,51%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67274</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57120</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77764</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>38,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>111124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142718</t>
+          <t>140636</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>6091</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10894</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13758</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21583</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>8386</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>20877</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,39%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,53%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3154</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10809</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>28538</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3715</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1356</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8231</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5501</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>2771</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5955</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3878</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173874</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173874</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173874</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>164040</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>164040</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>164040</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173874</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173874</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173874</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>178088</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>162717</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>191845</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,23%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>58,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>163495</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148993</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>177753</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>149545</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>178287</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>178088</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>162006</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>191181</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>53,88%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320716</t>
+          <t>321747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>364353</t>
+          <t>361939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,73%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>124687</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111956</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139783</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>42,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>126599</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>110896</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>140418</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>111357</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>140956</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,7%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>44,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>124687</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>111806</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139177</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>230053</t>
+          <t>232519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271028</t>
+          <t>271608</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,82%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22181</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>15281</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>31175</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,43%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>23158</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>16158</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>32227</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>15669</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>31744</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,26%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>22181</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>16184</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30314</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34678</t>
+          <t>35106</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57100</t>
+          <t>57354</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9936</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3715</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9142</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1424</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8542</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4946</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2142</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9856</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1925</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5054</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3408</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>481</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>330548</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>330548</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>330548</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>453</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>318893</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>318893</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>318893</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>330548</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>330548</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>330548</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>105040</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>94133</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>115923</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,93%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>109224</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>97854</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>119903</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97391</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>120210</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>59,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>53,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>105040</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>94054</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>116436</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,93%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>198510</t>
+          <t>199997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>229795</t>
+          <t>228459</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58868</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47104</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68619</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>37,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>61448</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>51155</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72915</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51027</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>72550</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>33,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,97%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58868</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48203</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69806</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,47%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106406</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134712</t>
+          <t>135056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8442</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19983</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,02%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>10037</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5571</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16456</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6287</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15810</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>13054</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8163</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19330</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32838</t>
+          <t>30846</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7133</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2185</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6334</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5848</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10182</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5726,107 +5726,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5509</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1503</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5152</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5291</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>181312</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>181312</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>181312</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>263</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>182894</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>182894</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>182894</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>181312</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>181312</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>181312</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95653</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84522</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>107198</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87121</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>77101</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>98115</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>76077</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,2%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,67%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>95653</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84055</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>107279</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167135</t>
+          <t>167191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199388</t>
+          <t>198055</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58711</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>48724</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69793</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>28,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>40,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68331</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58637</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>78660</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58579</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>79146</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,46%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58711</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>47781</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69249</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111252</t>
+          <t>112439</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>143974</t>
+          <t>143355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>13256</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8320</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20178</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10645</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6356</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17173</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5896</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>16595</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,26%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>10,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>13256</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7817</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19823</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16751</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32430</t>
+          <t>32741</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3766</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1731</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5888</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3766</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8432</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -6413,67 +6413,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5510</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>2317</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6293</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2051</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>660</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6742</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>9182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173437</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173437</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173437</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170145</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170145</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170145</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173437</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173437</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173437</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>200694</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>184646</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>215639</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>196345</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>181307</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>211832</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>181412</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>213035</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>200694</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>185812</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>216843</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373451</t>
+          <t>375575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>420754</t>
+          <t>419851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117579</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>104214</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>133825</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>129779</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>116219</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>145909</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>114745</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145077</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>36,76%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,92%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117579</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>102355</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>130885</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224757</t>
+          <t>226244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269772</t>
+          <t>273048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>26310</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19079</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35593</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>20682</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>14322</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28857</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>14473</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>29576</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,86%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>26310</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>18576</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>35018</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>37595</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>59956</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12207</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3916</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8701</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8524</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>3143</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>11926</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>17027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3554</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8380</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2317</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6163</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3554</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>12167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>354749</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>354749</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>354749</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>505</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>353039</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>353039</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>353039</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>354749</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>354749</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>354749</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
